--- a/project-context/TerminalGrafica/whatsapp-rag/Catalogo-TG-v4-wip.xlsx
+++ b/project-context/TerminalGrafica/whatsapp-rag/Catalogo-TG-v4-wip.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="981">
   <si>
     <t xml:space="preserve">CÓMO CARGAR PRODUCTOS NUEVOS</t>
   </si>
@@ -2707,6 +2707,267 @@
   </si>
   <si>
     <t xml:space="preserve">escaneo de 0,5 metros de planos (activa el mínimo por trabajo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte x1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paquete de 1000 hojas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recargo fijo por modelo/diseño de corte recto a medida, no depende de la cantidad de piezas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$5.000 fijo por modelo (unidad original: "modelo de corte")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omitido del lote de limpieza v4 (sept-2026): no hay mecanismo de recargos en el motor (cotizar() devuelve un total escalar por material, no componentes sumables). Confirmar con TG si es un recargo POR TRABAJO (una vez, sin importar las piezas) antes de diseñarlo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte con forma sobre un impreso ya listo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-10 piezas: $10.000 TOTAL fijo (no por pieza). 11-50: $1.000/pieza. 51-100: $800/pieza. 101-500: $600/pieza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omitido del lote v4: el primer tramo es "precio total del tramo", una forma de cobro que el motor no tiene (cotizar() multiplicaría 5 × $10.000 = $50.000 en vez de $10.000, en silencio). Reemplaza a "Troquelado y corte a medida" ($50/unidad, sin mínimo), que existía en producción — el bot pierde esa cotización hasta que se resuelva el modo nuevo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talonarios de rifas numeradas correlativamente, 100 números por talonario, 10x7 cm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escala en NÚMEROS DE RIFA (no en talonarios), precio TOTAL por tramo: 100-249→$7.200 · 250-499→$9.600 · 500-999→$12.000 · 1.000-4.999→$18.000 · 5.000-9.999→$50.400 · 10.000+→$64.800.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mismo motivo que Troquelado: precio total del tramo, sin modo de cobro que lo exprese.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talonarios de rifas numeradas correlativamente, 100 números por talonario, 15x7 cm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escala en NÚMEROS DE RIFA, precio TOTAL por tramo: 100-249→$10.800 · 250-499→$13.200 · 500-999→$20.400 · 1.000-4.999→$31.200 · 5.000-9.999→$57.600 · 10.000+→$68.400.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte a medida en Obra 80 gr / Ilustracion brillo 150 gr / mate 240 gr / mate 300 gr / Opalina 240 gr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 productos (Productos filas 102-106): apuntan al material del PAPEL, no al recargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si se dejaran, el bot cotizaría solo el papel y se comería los $5.000 de recargo en silencio — peor que no tenerlos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se borran junto con el material Corte a medida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puntas redondeadas x100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paquete de 100 puntas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puntas redondeadas x500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paquete de 500 puntas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puntas redondeadas x1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paquete de 1000 puntas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra b/n x500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paquete de 500 folletos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra b/n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra b/n x1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paquete de 1000 folletos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra b/n x2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paquete de 2000 folletos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra b/n x3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paquete de 3000 folletos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra color x500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra color x1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra color x2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 obra color x3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 ilustración brillo x500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 ilustración brillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 ilustración brillo x1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 ilustración brillo x2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 ilustración brillo x3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redondeo de puntas sobre un impreso ya listo. Paquete de 500.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redondeo de puntas sobre un impreso ya listo. Paquete de 1000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000 folletos 10x15 cm papel obra b/n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm impresos en blanco y negro, papel obra 75 gr. El precio es por los 1000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000 folletos 10x15 cm papel obra b/n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm impresos en blanco y negro, papel obra 75 gr. El precio es por los 2000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 folletos 10x15 cm papel obra b/n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm impresos en blanco y negro, papel obra 75 gr. El precio es por los 3000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000 folletos 10x15 cm papel obra color inkjet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm impresos a color (inkjet), papel obra 75 gr. El precio es por los 1000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000 folletos 10x15 cm papel obra color inkjet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm impresos a color (inkjet), papel obra 75 gr. El precio es por los 2000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 folletos 10x15 cm papel obra color inkjet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm impresos a color (inkjet), papel obra 75 gr. El precio es por los 3000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000 folletos 10x15 cm papel ilustración brillo 150gr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm en papel ilustración brillo 150 gr, mejor calidad. El precio es por los 1000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000 folletos 10x15 cm papel ilustración brillo 150gr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm en papel ilustración brillo 150 gr, mejor calidad. El precio es por los 2000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 folletos 10x15 cm papel ilustración brillo 150gr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folletos 10x15 cm en papel ilustración brillo 150 gr, mejor calidad. El precio es por los 3000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos A1, 25% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel obra 90 g, por metro cuadrado, mínimo medio m2. Cobertura de color/relleno 25%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos A1, 50% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel obra 90 g, por metro cuadrado, mínimo medio m2. Cobertura de color/relleno 50%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos A1, 100% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel obra 90 g, por metro cuadrado, mínimo medio m2. Cobertura de color/relleno 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plotter papel vegetal, 25% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel vegetal (translúcido), por metro cuadrado, mínimo medio m2. Cobertura 25%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plotter papel vegetal, 50% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel vegetal (translúcido), por metro cuadrado, mínimo medio m2. Cobertura 50%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plotter papel vegetal, 100% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel vegetal (translúcido), por metro cuadrado, mínimo medio m2. Cobertura 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plotter papel 130gr recubierto/encapado, 25% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel 130 gr recubierto/encapado, por metro cuadrado, mínimo medio m2. Cobertura 25%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plotter papel 130gr recubierto/encapado, 50% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel 130 gr recubierto/encapado, por metro cuadrado, mínimo medio m2. Cobertura 50%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plotter papel 130gr recubierto/encapado, 100% cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos en papel 130 gr recubierto/encapado, por metro cuadrado, mínimo medio m2. Cobertura 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microperforado (solvente) para vidriera 1x1 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microperforado solvente para vidrieras: desde adentro se ve hacia afuera, desde afuera se ve la impresión. Otro proceso de impresión que el UV (no fusionar sin confirmar con Pedro). Se cotiza por metro cuadrado, mínimo medio m2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">microperforado solvente, vinilo para vidriera, vinilo que se ve de adentro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imanes personalizados para heladera y promoción. Los chicos se cobran por unidad y bajan de precio por cantidad; los troquelados a medida se cotizan por metro cuadrado, mínimo medio m2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresión de planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plotter papel 130gr recubierto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microperforado</t>
   </si>
 </sst>
 </file>
@@ -3956,6 +4217,17 @@
         <v>156</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="26" t="s">
+        <v>556</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>977</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>559</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C2:C600" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ese material no existe" error="Elegí un material de la lista desplegable. Si necesitás uno nuevo, agregalo primero en la hoja Materiales." promptTitle="Material base" prompt="El material que se cotiza cuando el cliente no pide una opción especial. Sale de la hoja Materiales." type="list" errorStyle="stop" operator="between">
@@ -5976,108 +6248,6 @@
         <v>449</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="B101" s="26" t="s">
-        <v>450</v>
-      </c>
-      <c r="C101" s="27" t="s">
-        <v>451</v>
-      </c>
-      <c r="D101" s="25" t="s">
-        <v>452</v>
-      </c>
-      <c r="H101" s="28" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B102" s="26" t="s">
-        <v>454</v>
-      </c>
-      <c r="C102" s="27" t="s">
-        <v>455</v>
-      </c>
-      <c r="D102" s="25" t="s">
-        <v>456</v>
-      </c>
-      <c r="H102" s="28" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B103" s="26" t="s">
-        <v>458</v>
-      </c>
-      <c r="C103" s="27" t="s">
-        <v>459</v>
-      </c>
-      <c r="D103" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="H103" s="28" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B104" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="C104" s="27" t="s">
-        <v>462</v>
-      </c>
-      <c r="D104" s="25" t="s">
-        <v>463</v>
-      </c>
-      <c r="H104" s="28" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B105" s="26" t="s">
-        <v>464</v>
-      </c>
-      <c r="C105" s="27" t="s">
-        <v>465</v>
-      </c>
-      <c r="D105" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="H105" s="28" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B106" s="26" t="s">
-        <v>467</v>
-      </c>
-      <c r="C106" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="D106" s="25" t="s">
-        <v>469</v>
-      </c>
-      <c r="H106" s="28" t="s">
-        <v>457</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" s="25" t="s">
         <v>145</v>
@@ -6945,7 +7115,7 @@
         <v>625</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>624</v>
+        <v>911</v>
       </c>
       <c r="H152" s="28" t="s">
         <v>626</v>
@@ -6981,7 +7151,7 @@
         <v>630</v>
       </c>
       <c r="D154" s="25" t="s">
-        <v>631</v>
+        <v>894</v>
       </c>
       <c r="H154" s="28" t="s">
         <v>632</v>
@@ -6999,7 +7169,7 @@
         <v>634</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>633</v>
+        <v>917</v>
       </c>
       <c r="H155" s="28" t="s">
         <v>635</v>
@@ -7019,7 +7189,7 @@
         <v>637</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>636</v>
+        <v>926</v>
       </c>
       <c r="H156" s="28" t="s">
         <v>635</v>
@@ -7039,7 +7209,7 @@
         <v>639</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>638</v>
+        <v>931</v>
       </c>
       <c r="H157" s="28" t="s">
         <v>640</v>
@@ -7168,46 +7338,6 @@
         <v>653</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="B164" s="26" t="s">
-        <v>656</v>
-      </c>
-      <c r="C164" s="27" t="s">
-        <v>657</v>
-      </c>
-      <c r="D164" s="25" t="s">
-        <v>658</v>
-      </c>
-      <c r="H164" s="28" t="s">
-        <v>659</v>
-      </c>
-      <c r="I164" s="28" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="B165" s="26" t="s">
-        <v>660</v>
-      </c>
-      <c r="C165" s="27" t="s">
-        <v>661</v>
-      </c>
-      <c r="D165" s="25" t="s">
-        <v>662</v>
-      </c>
-      <c r="H165" s="28" t="s">
-        <v>659</v>
-      </c>
-      <c r="I165" s="28" t="s">
-        <v>663</v>
-      </c>
-    </row>
     <row r="166">
       <c r="A166" s="25" t="s">
         <v>140</v>
@@ -7243,6 +7373,414 @@
         <v>669</v>
       </c>
       <c r="I167" s="28" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B168" s="26" t="s">
+        <v>913</v>
+      </c>
+      <c r="C168" s="27" t="s">
+        <v>936</v>
+      </c>
+      <c r="D168" s="25" t="s">
+        <v>913</v>
+      </c>
+      <c r="H168" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B169" s="26" t="s">
+        <v>915</v>
+      </c>
+      <c r="C169" s="27" t="s">
+        <v>937</v>
+      </c>
+      <c r="D169" s="25" t="s">
+        <v>915</v>
+      </c>
+      <c r="H169" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B170" s="26" t="s">
+        <v>938</v>
+      </c>
+      <c r="C170" s="27" t="s">
+        <v>939</v>
+      </c>
+      <c r="D170" s="25" t="s">
+        <v>920</v>
+      </c>
+      <c r="H170" t="s">
+        <v>635</v>
+      </c>
+      <c r="I170" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B171" s="26" t="s">
+        <v>940</v>
+      </c>
+      <c r="C171" s="27" t="s">
+        <v>941</v>
+      </c>
+      <c r="D171" s="25" t="s">
+        <v>922</v>
+      </c>
+      <c r="H171" t="s">
+        <v>635</v>
+      </c>
+      <c r="I171" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B172" s="26" t="s">
+        <v>942</v>
+      </c>
+      <c r="C172" s="27" t="s">
+        <v>943</v>
+      </c>
+      <c r="D172" s="25" t="s">
+        <v>924</v>
+      </c>
+      <c r="H172" t="s">
+        <v>635</v>
+      </c>
+      <c r="I172" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B173" s="26" t="s">
+        <v>944</v>
+      </c>
+      <c r="C173" s="27" t="s">
+        <v>945</v>
+      </c>
+      <c r="D173" s="25" t="s">
+        <v>928</v>
+      </c>
+      <c r="H173" t="s">
+        <v>635</v>
+      </c>
+      <c r="I173" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B174" s="26" t="s">
+        <v>946</v>
+      </c>
+      <c r="C174" s="27" t="s">
+        <v>947</v>
+      </c>
+      <c r="D174" s="25" t="s">
+        <v>929</v>
+      </c>
+      <c r="H174" t="s">
+        <v>635</v>
+      </c>
+      <c r="I174" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B175" s="26" t="s">
+        <v>948</v>
+      </c>
+      <c r="C175" s="27" t="s">
+        <v>949</v>
+      </c>
+      <c r="D175" s="25" t="s">
+        <v>930</v>
+      </c>
+      <c r="H175" t="s">
+        <v>635</v>
+      </c>
+      <c r="I175" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B176" s="26" t="s">
+        <v>950</v>
+      </c>
+      <c r="C176" s="27" t="s">
+        <v>951</v>
+      </c>
+      <c r="D176" s="25" t="s">
+        <v>933</v>
+      </c>
+      <c r="H176" t="s">
+        <v>640</v>
+      </c>
+      <c r="I176" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B177" s="26" t="s">
+        <v>952</v>
+      </c>
+      <c r="C177" s="27" t="s">
+        <v>953</v>
+      </c>
+      <c r="D177" s="25" t="s">
+        <v>934</v>
+      </c>
+      <c r="H177" t="s">
+        <v>640</v>
+      </c>
+      <c r="I177" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B178" s="26" t="s">
+        <v>954</v>
+      </c>
+      <c r="C178" s="27" t="s">
+        <v>955</v>
+      </c>
+      <c r="D178" s="25" t="s">
+        <v>935</v>
+      </c>
+      <c r="H178" t="s">
+        <v>640</v>
+      </c>
+      <c r="I178" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B179" s="26" t="s">
+        <v>956</v>
+      </c>
+      <c r="C179" s="27" t="s">
+        <v>957</v>
+      </c>
+      <c r="D179" s="25" t="s">
+        <v>715</v>
+      </c>
+      <c r="E179" s="32" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="F179" s="32" t="n">
+        <v>84.1</v>
+      </c>
+      <c r="H179" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B180" s="26" t="s">
+        <v>958</v>
+      </c>
+      <c r="C180" s="27" t="s">
+        <v>959</v>
+      </c>
+      <c r="D180" s="25" t="s">
+        <v>716</v>
+      </c>
+      <c r="E180" s="32" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="F180" s="32" t="n">
+        <v>84.1</v>
+      </c>
+      <c r="H180" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B181" s="26" t="s">
+        <v>960</v>
+      </c>
+      <c r="C181" s="27" t="s">
+        <v>961</v>
+      </c>
+      <c r="D181" s="25" t="s">
+        <v>717</v>
+      </c>
+      <c r="E181" s="32" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="F181" s="32" t="n">
+        <v>84.1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B182" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="C182" s="27" t="s">
+        <v>963</v>
+      </c>
+      <c r="D182" s="25" t="s">
+        <v>718</v>
+      </c>
+      <c r="H182" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B183" s="26" t="s">
+        <v>964</v>
+      </c>
+      <c r="C183" s="27" t="s">
+        <v>965</v>
+      </c>
+      <c r="D183" s="25" t="s">
+        <v>719</v>
+      </c>
+      <c r="H183" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B184" s="26" t="s">
+        <v>966</v>
+      </c>
+      <c r="C184" s="27" t="s">
+        <v>967</v>
+      </c>
+      <c r="D184" s="25" t="s">
+        <v>720</v>
+      </c>
+      <c r="H184" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B185" s="26" t="s">
+        <v>968</v>
+      </c>
+      <c r="C185" s="27" t="s">
+        <v>969</v>
+      </c>
+      <c r="D185" s="25" t="s">
+        <v>721</v>
+      </c>
+      <c r="H185" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B186" s="26" t="s">
+        <v>970</v>
+      </c>
+      <c r="C186" s="27" t="s">
+        <v>971</v>
+      </c>
+      <c r="D186" s="25" t="s">
+        <v>722</v>
+      </c>
+      <c r="H186" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B187" s="26" t="s">
+        <v>972</v>
+      </c>
+      <c r="C187" s="27" t="s">
+        <v>973</v>
+      </c>
+      <c r="D187" s="25" t="s">
+        <v>723</v>
+      </c>
+      <c r="H187" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B188" s="26" t="s">
+        <v>974</v>
+      </c>
+      <c r="C188" s="27" t="s">
+        <v>975</v>
+      </c>
+      <c r="D188" s="25" t="s">
+        <v>728</v>
+      </c>
+      <c r="E188" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="F188" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H188" t="s">
+        <v>976</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -8979,7 +9517,7 @@
         <v>358</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C95" s="32" t="n">
         <v>1</v>
@@ -9323,6 +9861,9 @@
       <c r="F116" s="28" t="s">
         <v>706</v>
       </c>
+      <c r="L116" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="15">
       <c r="A117" s="26" t="s">
@@ -9357,6 +9898,9 @@
       <c r="F118" s="28" t="s">
         <v>706</v>
       </c>
+      <c r="L118" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="15">
       <c r="A119" s="26" t="s">
@@ -10008,101 +10552,6 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="26" t="s">
-        <v>709</v>
-      </c>
-      <c r="B155" s="32" t="s">
-        <v>710</v>
-      </c>
-      <c r="C155" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" s="33" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G155" s="28" t="s">
-        <v>711</v>
-      </c>
-      <c r="K155" s="28" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="B156" s="32" t="s">
-        <v>695</v>
-      </c>
-      <c r="C156" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D156" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E156" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G156" s="28" t="s">
-        <v>712</v>
-      </c>
-      <c r="K156" s="28" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="B157" s="32" t="s">
-        <v>695</v>
-      </c>
-      <c r="C157" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="D157" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="E157" s="33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K157" s="28" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="B158" s="32" t="s">
-        <v>695</v>
-      </c>
-      <c r="C158" s="32" t="n">
-        <v>51</v>
-      </c>
-      <c r="D158" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="E158" s="33" t="n">
-        <v>800</v>
-      </c>
-      <c r="K158" s="28" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="B159" s="32" t="s">
-        <v>695</v>
-      </c>
-      <c r="C159" s="32" t="n">
-        <v>101</v>
-      </c>
-      <c r="D159" s="28" t="n">
-        <v>500</v>
-      </c>
-      <c r="E159" s="33" t="n">
-        <v>600</v>
-      </c>
-      <c r="K159" s="28" t="n"/>
-    </row>
     <row r="160">
       <c r="A160" s="26" t="s">
         <v>470</v>
@@ -10625,6 +11074,9 @@
       <c r="F187" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L187" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="26" t="s">
@@ -10642,6 +11094,9 @@
       <c r="F188" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L188" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="26" t="s">
@@ -10659,6 +11114,9 @@
       <c r="F189" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L189" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="26" t="s">
@@ -10676,6 +11134,9 @@
       <c r="F190" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L190" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="26" t="s">
@@ -10693,6 +11154,9 @@
       <c r="F191" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L191" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="26" t="s">
@@ -10710,6 +11174,9 @@
       <c r="F192" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L192" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="26" t="s">
@@ -10727,6 +11194,9 @@
       <c r="F193" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L193" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="26" t="s">
@@ -10744,6 +11214,9 @@
       <c r="F194" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L194" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="26" t="s">
@@ -10761,6 +11234,9 @@
       <c r="F195" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L195" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="26" t="s">
@@ -10778,6 +11254,9 @@
       <c r="F196" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L196" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="26" t="s">
@@ -10795,6 +11274,9 @@
       <c r="F197" s="28" t="n">
         <v>0.5</v>
       </c>
+      <c r="L197" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="26" t="s">
@@ -11000,6 +11482,9 @@
       <c r="G208" s="28" t="s">
         <v>729</v>
       </c>
+      <c r="L208" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="26" t="s">
@@ -11721,56 +12206,6 @@
       <c r="K245" s="28" t="n"/>
       <c r="L245" s="28" t="n"/>
     </row>
-    <row r="246">
-      <c r="A246" s="26" t="s">
-        <v>624</v>
-      </c>
-      <c r="B246" s="32" t="s">
-        <v>748</v>
-      </c>
-      <c r="C246" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E246" s="33" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K246" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="L246" s="28" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="26" t="s">
-        <v>624</v>
-      </c>
-      <c r="B247" s="32" t="s">
-        <v>749</v>
-      </c>
-      <c r="C247" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E247" s="33" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K247" s="28" t="n"/>
-      <c r="L247" s="28" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="26" t="s">
-        <v>624</v>
-      </c>
-      <c r="B248" s="32" t="s">
-        <v>750</v>
-      </c>
-      <c r="C248" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E248" s="33" t="n">
-        <v>7000</v>
-      </c>
-      <c r="K248" s="28" t="n"/>
-      <c r="L248" s="28" t="n"/>
-    </row>
     <row r="249">
       <c r="A249" s="26" t="s">
         <v>627</v>
@@ -11791,10 +12226,10 @@
     </row>
     <row r="250">
       <c r="A250" s="26" t="s">
-        <v>631</v>
+        <v>894</v>
       </c>
       <c r="B250" s="32" t="s">
-        <v>752</v>
+        <v>895</v>
       </c>
       <c r="C250" s="32" t="n">
         <v>1</v>
@@ -11806,228 +12241,6 @@
         <v>144</v>
       </c>
       <c r="L250" s="28" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="26" t="s">
-        <v>633</v>
-      </c>
-      <c r="B251" s="32" t="s">
-        <v>749</v>
-      </c>
-      <c r="C251" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E251" s="33" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K251" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="L251" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="26" t="s">
-        <v>633</v>
-      </c>
-      <c r="B252" s="32" t="s">
-        <v>750</v>
-      </c>
-      <c r="C252" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E252" s="33" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K252" s="28" t="n"/>
-      <c r="L252" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="26" t="s">
-        <v>633</v>
-      </c>
-      <c r="B253" s="32" t="s">
-        <v>754</v>
-      </c>
-      <c r="C253" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E253" s="33" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K253" s="28" t="n"/>
-      <c r="L253" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="26" t="s">
-        <v>633</v>
-      </c>
-      <c r="B254" s="32" t="s">
-        <v>755</v>
-      </c>
-      <c r="C254" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E254" s="33" t="n">
-        <v>49000</v>
-      </c>
-      <c r="K254" s="28" t="n"/>
-      <c r="L254" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="26" t="s">
-        <v>636</v>
-      </c>
-      <c r="B255" s="32" t="s">
-        <v>749</v>
-      </c>
-      <c r="C255" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E255" s="33" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K255" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="L255" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="26" t="s">
-        <v>636</v>
-      </c>
-      <c r="B256" s="32" t="s">
-        <v>750</v>
-      </c>
-      <c r="C256" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E256" s="33" t="n">
-        <v>27000</v>
-      </c>
-      <c r="K256" s="28" t="n"/>
-      <c r="L256" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="26" t="s">
-        <v>636</v>
-      </c>
-      <c r="B257" s="32" t="s">
-        <v>754</v>
-      </c>
-      <c r="C257" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E257" s="33" t="n">
-        <v>40000</v>
-      </c>
-      <c r="K257" s="28" t="n"/>
-      <c r="L257" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="26" t="s">
-        <v>636</v>
-      </c>
-      <c r="B258" s="32" t="s">
-        <v>755</v>
-      </c>
-      <c r="C258" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E258" s="33" t="n">
-        <v>59000</v>
-      </c>
-      <c r="K258" s="28" t="n"/>
-      <c r="L258" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="26" t="s">
-        <v>638</v>
-      </c>
-      <c r="B259" s="32" t="s">
-        <v>749</v>
-      </c>
-      <c r="C259" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E259" s="33" t="n">
-        <v>66000</v>
-      </c>
-      <c r="K259" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="L259" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="26" t="s">
-        <v>638</v>
-      </c>
-      <c r="B260" s="32" t="s">
-        <v>750</v>
-      </c>
-      <c r="C260" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E260" s="33" t="n">
-        <v>120000</v>
-      </c>
-      <c r="K260" s="28" t="n"/>
-      <c r="L260" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="26" t="s">
-        <v>638</v>
-      </c>
-      <c r="B261" s="32" t="s">
-        <v>754</v>
-      </c>
-      <c r="C261" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E261" s="33" t="n">
-        <v>223000</v>
-      </c>
-      <c r="K261" s="28" t="n"/>
-      <c r="L261" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="26" t="s">
-        <v>638</v>
-      </c>
-      <c r="B262" s="32" t="s">
-        <v>755</v>
-      </c>
-      <c r="C262" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E262" s="33" t="n">
-        <v>300000</v>
-      </c>
-      <c r="K262" s="28" t="n"/>
-      <c r="L262" s="28" t="s">
-        <v>753</v>
-      </c>
     </row>
     <row r="263">
       <c r="A263" s="26" t="s">
@@ -12515,232 +12728,6 @@
       <c r="K286" s="28" t="n"/>
       <c r="L286" s="28" t="n"/>
     </row>
-    <row r="287">
-      <c r="A287" s="26" t="s">
-        <v>658</v>
-      </c>
-      <c r="B287" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C287" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="D287" t="n">
-        <v>249</v>
-      </c>
-      <c r="E287" s="33" t="n">
-        <v>7200</v>
-      </c>
-      <c r="K287" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="L287" s="28" t="n"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="26" t="s">
-        <v>658</v>
-      </c>
-      <c r="B288" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C288" s="32" t="n">
-        <v>250</v>
-      </c>
-      <c r="D288" t="n">
-        <v>499</v>
-      </c>
-      <c r="E288" s="33" t="n">
-        <v>9600</v>
-      </c>
-      <c r="K288" s="28" t="n"/>
-      <c r="L288" s="28" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="26" t="s">
-        <v>658</v>
-      </c>
-      <c r="B289" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C289" s="32" t="n">
-        <v>500</v>
-      </c>
-      <c r="D289" t="n">
-        <v>999</v>
-      </c>
-      <c r="E289" s="33" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K289" s="28" t="n"/>
-      <c r="L289" s="28" t="n"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="26" t="s">
-        <v>658</v>
-      </c>
-      <c r="B290" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C290" s="32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D290" t="n">
-        <v>4999</v>
-      </c>
-      <c r="E290" s="33" t="n">
-        <v>18000</v>
-      </c>
-      <c r="K290" s="28" t="n"/>
-      <c r="L290" s="28" t="n"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="26" t="s">
-        <v>658</v>
-      </c>
-      <c r="B291" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C291" s="32" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D291" t="n">
-        <v>9999</v>
-      </c>
-      <c r="E291" s="33" t="n">
-        <v>50400</v>
-      </c>
-      <c r="K291" s="28" t="n"/>
-      <c r="L291" s="28" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="26" t="s">
-        <v>658</v>
-      </c>
-      <c r="B292" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C292" s="32" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E292" s="33" t="n">
-        <v>64800</v>
-      </c>
-      <c r="K292" s="28" t="n"/>
-      <c r="L292" s="28" t="n"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="26" t="s">
-        <v>662</v>
-      </c>
-      <c r="B293" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C293" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="D293" t="n">
-        <v>249</v>
-      </c>
-      <c r="E293" s="33" t="n">
-        <v>10800</v>
-      </c>
-      <c r="K293" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="L293" s="28" t="n"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="26" t="s">
-        <v>662</v>
-      </c>
-      <c r="B294" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C294" s="32" t="n">
-        <v>250</v>
-      </c>
-      <c r="D294" t="n">
-        <v>499</v>
-      </c>
-      <c r="E294" s="33" t="n">
-        <v>13200</v>
-      </c>
-      <c r="K294" s="28" t="n"/>
-      <c r="L294" s="28" t="n"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="26" t="s">
-        <v>662</v>
-      </c>
-      <c r="B295" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C295" s="32" t="n">
-        <v>500</v>
-      </c>
-      <c r="D295" t="n">
-        <v>999</v>
-      </c>
-      <c r="E295" s="33" t="n">
-        <v>20400</v>
-      </c>
-      <c r="K295" s="28" t="n"/>
-      <c r="L295" s="28" t="n"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="26" t="s">
-        <v>662</v>
-      </c>
-      <c r="B296" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C296" s="32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D296" t="n">
-        <v>4999</v>
-      </c>
-      <c r="E296" s="33" t="n">
-        <v>31200</v>
-      </c>
-      <c r="K296" s="28" t="n"/>
-      <c r="L296" s="28" t="n"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="26" t="s">
-        <v>662</v>
-      </c>
-      <c r="B297" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C297" s="32" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D297" t="n">
-        <v>9999</v>
-      </c>
-      <c r="E297" s="33" t="n">
-        <v>57600</v>
-      </c>
-      <c r="K297" s="28" t="n"/>
-      <c r="L297" s="28" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="26" t="s">
-        <v>662</v>
-      </c>
-      <c r="B298" s="32" t="s">
-        <v>757</v>
-      </c>
-      <c r="C298" s="32" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E298" s="33" t="n">
-        <v>68400</v>
-      </c>
-      <c r="K298" s="28" t="n"/>
-      <c r="L298" s="28" t="n"/>
-    </row>
     <row r="299">
       <c r="A299" s="26" t="s">
         <v>664</v>
@@ -12776,6 +12763,261 @@
         <v>144</v>
       </c>
       <c r="L300" s="28" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="26" t="s">
+        <v>911</v>
+      </c>
+      <c r="B301" s="32" t="s">
+        <v>912</v>
+      </c>
+      <c r="E301" s="33" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K301" t="s">
+        <v>144</v>
+      </c>
+      <c r="L301" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="26" t="s">
+        <v>913</v>
+      </c>
+      <c r="B302" s="32" t="s">
+        <v>914</v>
+      </c>
+      <c r="E302" s="33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K302" t="s">
+        <v>144</v>
+      </c>
+      <c r="L302" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="26" t="s">
+        <v>915</v>
+      </c>
+      <c r="B303" s="32" t="s">
+        <v>916</v>
+      </c>
+      <c r="E303" s="33" t="n">
+        <v>7000</v>
+      </c>
+      <c r="K303" t="s">
+        <v>144</v>
+      </c>
+      <c r="L303" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="26" t="s">
+        <v>917</v>
+      </c>
+      <c r="B304" s="32" t="s">
+        <v>918</v>
+      </c>
+      <c r="E304" s="33" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K304" t="s">
+        <v>144</v>
+      </c>
+      <c r="L304" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="26" t="s">
+        <v>920</v>
+      </c>
+      <c r="B305" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="E305" s="33" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K305" t="s">
+        <v>144</v>
+      </c>
+      <c r="L305" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="26" t="s">
+        <v>922</v>
+      </c>
+      <c r="B306" s="32" t="s">
+        <v>923</v>
+      </c>
+      <c r="E306" s="33" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K306" t="s">
+        <v>144</v>
+      </c>
+      <c r="L306" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="26" t="s">
+        <v>924</v>
+      </c>
+      <c r="B307" s="32" t="s">
+        <v>925</v>
+      </c>
+      <c r="E307" s="33" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K307" t="s">
+        <v>144</v>
+      </c>
+      <c r="L307" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="26" t="s">
+        <v>926</v>
+      </c>
+      <c r="B308" s="32" t="s">
+        <v>918</v>
+      </c>
+      <c r="E308" s="33" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K308" t="s">
+        <v>144</v>
+      </c>
+      <c r="L308" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="B309" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="E309" s="33" t="n">
+        <v>27000</v>
+      </c>
+      <c r="K309" t="s">
+        <v>144</v>
+      </c>
+      <c r="L309" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="26" t="s">
+        <v>929</v>
+      </c>
+      <c r="B310" s="32" t="s">
+        <v>923</v>
+      </c>
+      <c r="E310" s="33" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K310" t="s">
+        <v>144</v>
+      </c>
+      <c r="L310" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="26" t="s">
+        <v>930</v>
+      </c>
+      <c r="B311" s="32" t="s">
+        <v>925</v>
+      </c>
+      <c r="E311" s="33" t="n">
+        <v>59000</v>
+      </c>
+      <c r="K311" t="s">
+        <v>144</v>
+      </c>
+      <c r="L311" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="26" t="s">
+        <v>931</v>
+      </c>
+      <c r="B312" s="32" t="s">
+        <v>918</v>
+      </c>
+      <c r="E312" s="33" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K312" t="s">
+        <v>144</v>
+      </c>
+      <c r="L312" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="26" t="s">
+        <v>933</v>
+      </c>
+      <c r="B313" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="E313" s="33" t="n">
+        <v>120000</v>
+      </c>
+      <c r="K313" t="s">
+        <v>144</v>
+      </c>
+      <c r="L313" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="26" t="s">
+        <v>934</v>
+      </c>
+      <c r="B314" s="32" t="s">
+        <v>923</v>
+      </c>
+      <c r="E314" s="33" t="n">
+        <v>223000</v>
+      </c>
+      <c r="K314" t="s">
+        <v>144</v>
+      </c>
+      <c r="L314" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="26" t="s">
+        <v>935</v>
+      </c>
+      <c r="B315" s="32" t="s">
+        <v>925</v>
+      </c>
+      <c r="E315" s="33" t="n">
+        <v>300000</v>
+      </c>
+      <c r="K315" t="s">
+        <v>144</v>
+      </c>
+      <c r="L315" t="s">
+        <v>932</v>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -12812,6 +13054,76 @@
         <v>759</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C2" t="s">
+        <v>897</v>
+      </c>
+      <c r="D2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B3" t="s">
+        <v>899</v>
+      </c>
+      <c r="C3" t="s">
+        <v>900</v>
+      </c>
+      <c r="D3" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>658</v>
+      </c>
+      <c r="B4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>662</v>
+      </c>
+      <c r="B5" t="s">
+        <v>905</v>
+      </c>
+      <c r="C5" t="s">
+        <v>906</v>
+      </c>
+      <c r="D5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>907</v>
+      </c>
+      <c r="B6" t="s">
+        <v>908</v>
+      </c>
+      <c r="C6" t="s">
+        <v>909</v>
+      </c>
+      <c r="D6" t="s">
+        <v>910</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>

--- a/project-context/TerminalGrafica/whatsapp-rag/Catalogo-TG-v4-wip.xlsx
+++ b/project-context/TerminalGrafica/whatsapp-rag/Catalogo-TG-v4-wip.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="1053">
   <si>
     <t xml:space="preserve">CÓMO CARGAR PRODUCTOS NUEVOS</t>
   </si>
@@ -2968,6 +2968,222 @@
   </si>
   <si>
     <t xml:space="preserve">Microperforado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÓMO USAR ESTE ARCHIVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este archivo NO tiene precios cerrados por cantidad. Tiene el framework para calcular cualquier cantidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada producto dice de qué material se hace. Las medidas del catálogo son REFERENCIAS: se cotiza CUALQUIER medida que pida el cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La primera parte explica cómo COTIZAR (leer). La segunda, cómo CARGAR cosas nuevas (escribir).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">═══ PARTE 1: CÓMO COTIZAR ═══</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MODO "pliego" (stickers y etiquetas en papel autoadhesivo u OPP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Rinde: cuántas piezas entran en una unidad de cobro. Se calcula con la geometría del</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   MATERIAL (hoja Materiales: 'Área útil ancho/alto (cm)' y 'Separación (cm)'):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   columnas × filas que entran = floor((útil + sep) ÷ (pieza + sep)) en cada eje,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   probando las DOS orientaciones y tomando la que rinde más. Vale CUALQUIER medida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Ejemplo: pieza de 12x8 troquelada (área útil 28x44, separación 0,3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Acostada: 28,3÷12,3 = 2 columnas × 44,3÷8,3 = 5 filas = 10. Parada: 3 × 3 = 9. → 10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Si el rinde da 0 (la pieza no entra en ninguna orientación), NO cotizar: derivar a consulta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Pliegos necesarios = cantidad pedida ÷ piezas por pliego, redondeando HACIA ARRIBA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Buscar en Materiales el tramo que contiene esa cantidad de PLIEGOS (no de piezas).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Total = pliegos × el precio de ese tramo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Ejemplo: 250 stickers 3x3. Entran 104 por pliego. 250 ÷ 104 = 2,4 → 3 pliegos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   3 pliegos cae en el tramo 2-10 → $2.200. Total = 3 × 2.200 = $6.600.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   OJO: el tramo se busca por PLIEGOS. Con 3 pliegos el tramo es 2-10, no el de 101+.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MODO "m2" (vinilos, lonas, carteles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. m2 de una pieza = (ancho × alto) ÷ 10.000. Las medidas están en centímetros. Vale CUALQUIER medida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. m2 totales = m2 de una pieza × cantidad pedida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Si el resultado es menor al mínimo facturable del material, se cobra el mínimo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Total = m2 facturados × el precio por m2 del material.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Ejemplo: 100 stickers en vinilo UV de 5x5. Una pieza = 25 ÷ 10.000 = 0,0025 m2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   100 piezas = 0,25 m2. Es menos que el mínimo de 0,5 → se cobran 0,5 m2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Total = 0,5 × 28.000 = $14.000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿CUÁL DE LOS DOS MODOS?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo decide la columna "Unidad" del MATERIAL, no el producto. Si empieza con "pliego" → modo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pliego. Si es "m2" → modo m2. El producto no dice el modo en ningún lado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL FINAL, SIEMPRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Aplicar el mínimo por trabajo de la hoja Parámetros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Redondear al múltiplo indicado en Parámetros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">═══ PARTE 2: CÓMO CARGAR COSAS NUEVAS ═══</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parámetros  — mínimo por trabajo, redondeo, moneda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casos de prueba — NO se usa para cotizar. Verifica que el bot calcula bien.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_listas     — hoja OCULTA. Alimenta los desplegables. Ver abajo, hay que tocarla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">que ya existen. Si cargás el producto primero, el desplegable no va a tener qué ofrecerte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (Material de PLIEGO: cargar también 'Área útil ancho/alto (cm)' y 'Separación (cm)',</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   una sola vez, en la primera fila del material.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASO 3 — Registrar los dos en _listas (la hoja oculta). SIN ESTE PASO LOS DESPLEGABLES NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   LOS OFRECEN. Mostrar la hoja (clic derecho en las pestañas → Mostrar) y agregar:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   columna A → el material nuevo   ·   columna B → la colección nueva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Van en la primera fila libre de cada columna, sin dejar huecos en el medio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASO 4 — Producto. En la hoja Productos, primera fila libre:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Material: Imán flexible | Ancho: 8 | Alto: 5 | Piezas por unidad de cobro: (vacío, es modo m2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calcula solo, con la fórmula de la PARTE 1: el visor lo calcula para las medidas de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">referencia y el bot para cualquier otra medida que pida el cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manda sobre el cálculo, y el visor avisa si no coincide con la geometría.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los desplegables y la validación cubren un rango fijo. Hoy hay lugar para:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Productos: hasta la fila 72 · Materiales en _listas: hasta A42 · Colecciones: hasta B35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasado eso el desplegable deja de funcionar SIN AVISAR. Si se llega al tope, hay que extender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el rango (Datos → Validación) y el nombre definido, o avisar para que lo hagamos nosotros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNA UNIDAD DE COBRO NUEVA (algo que no se cobra por pliego ni por m2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoy existen dos: 'pliego A3' y 'm2'. Cada una tiene su fórmula en la PARTE 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se puede agregar otra (por unidad, por metro lineal, por hora), y el archivo la acepta:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el precio se muestra bien solo. Lo que NO existe es la fórmula para cotizarla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si agregás una unidad nueva, hay que escribir su regla de cálculo acá abajo, en la PARTE 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin eso el bot no sabe cómo pasar de lo que pide el cliente al total, y va a improvisar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Ejemplo — cobrar por unidad suelta:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1. Agregar el material con Unidad: unidad (ej. Imán suelto, $900, Desde 1, Hasta vacío).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   2. Agregar acá una sección MODO "unidad": Total = cantidad pedida × precio del tramo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   3. El producto NO lleva rinde ni el material 'Mínimo facturable'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si tu unidad nueva se cobra distinto, NO la llames empezando con 'pliego' ni con 'm2':</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   y queda sin fórmula. Para metros cuadrados escribí siempre 'm2'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Material de modo pliego sin geometría: no hay de dónde calcular el rinde. El visor lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  avisa al cargar el archivo; hasta cargarla, el bot no puede cotizar ese material.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Rinde cargado a mano Y geometría que no coinciden: gana el dato cargado y el visor avisa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Pieza más grande que el área útil: rinde 0. Se deriva a consulta, nunca se inventa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Tramos superpuestos (1-10 y 5-20): se aplica el primero que coincide, y puede no ser el que querías.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardar el archivo y volver a cargarlo en el visor de chunks para ver qué va a leer el bot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los cambios NO llegan al bot hasta que se ingesta desde ahí.</t>
   </si>
 </sst>
 </file>
@@ -3409,651 +3625,648 @@
     <col width="105" customWidth="1" style="28" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.35" customHeight="1" s="15">
+    <row r="1">
       <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="15"/>
-    <row r="3" ht="15" customHeight="1" s="15">
-      <c r="A3" s="17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="15">
-      <c r="A4" s="17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="15"/>
-    <row r="6" ht="15" customHeight="1" s="15">
-      <c r="A6" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="15">
-      <c r="A7" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="15"/>
-    <row r="9" ht="15" customHeight="1" s="15">
-      <c r="A9" s="18" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="16" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="16" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="16" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="16" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="16" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="16" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="16" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="16" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="16" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="15"/>
-    <row r="11" ht="15" customHeight="1" s="15">
-      <c r="A11" s="17" t="s">
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="15">
-      <c r="A12" s="17" t="s">
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="15">
-      <c r="A13" s="17" t="s">
+    <row r="55">
+      <c r="A55" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="15">
-      <c r="A14" s="17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="15">
-      <c r="A15" s="17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="15">
-      <c r="A17" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="15"/>
-    <row r="19" ht="15" customHeight="1" s="15">
-      <c r="A19" s="18" t="s">
+    <row r="56">
+      <c r="A56" s="16" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="15"/>
-    <row r="21" ht="15" customHeight="1" s="15">
-      <c r="A21" s="17" t="s">
+    <row r="60">
+      <c r="A60" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="15">
-      <c r="A22" s="17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="15"/>
-    <row r="24" ht="15" customHeight="1" s="15">
-      <c r="A24" s="18" t="s">
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="16" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="15"/>
-    <row r="26" ht="15" customHeight="1" s="15">
-      <c r="A26" s="17" t="s">
+    <row r="64">
+      <c r="A64" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="15"/>
-    <row r="28" ht="15" customHeight="1" s="15">
-      <c r="A28" s="17" t="s">
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="15">
-      <c r="A29" s="19" t="s">
+    <row r="67">
+      <c r="A67" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="15">
-      <c r="A30" s="19" t="s">
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="15">
-      <c r="A31" s="19" t="s">
+    <row r="70">
+      <c r="A70" s="16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="15">
-      <c r="A32" s="19" t="s">
+    <row r="71">
+      <c r="A71" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="15"/>
-    <row r="34" ht="15" customHeight="1" s="15">
-      <c r="A34" s="17" t="s">
+    <row r="72">
+      <c r="A72" s="16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="15">
-      <c r="A35" s="19" t="s">
+    <row r="73">
+      <c r="A73" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="15">
-      <c r="A36" s="19" t="s">
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="15"/>
-    <row r="38" ht="15" customHeight="1" s="15">
-      <c r="A38" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="15">
-      <c r="A39" s="19" t="s">
+    <row r="76">
+      <c r="A76" s="16" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="16" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="16" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="15">
-      <c r="A40" s="19" t="s">
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="16" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="15">
-      <c r="A41" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="15"/>
-    <row r="43" ht="15" customHeight="1" s="15">
-      <c r="A43" s="18" t="s">
+    <row r="87">
+      <c r="A87" s="16" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="15"/>
-    <row r="45" ht="15" customHeight="1" s="15">
-      <c r="A45" s="17" t="s">
+    <row r="89">
+      <c r="A89" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="15">
-      <c r="A46" s="19" t="s">
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="15">
-      <c r="A47" s="19" t="s">
+    <row r="92">
+      <c r="A92" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="15">
-      <c r="A48" s="19" t="s">
+    <row r="93">
+      <c r="A93" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="15">
-      <c r="A49" s="19" t="s">
+    <row r="94">
+      <c r="A94" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="15"/>
-    <row r="51" ht="15" customHeight="1" s="15">
-      <c r="A51" s="17" t="s">
+    <row r="95">
+      <c r="A95" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="15"/>
-    <row r="53" ht="15" customHeight="1" s="15">
-      <c r="A53" s="18" t="s">
+    <row r="96">
+      <c r="A96" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="15"/>
-    <row r="55" ht="15" customHeight="1" s="15">
-      <c r="A55" s="17" t="s">
+    <row r="97">
+      <c r="A97" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="15">
-      <c r="A56" s="19" t="s">
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="15">
-      <c r="A57" s="19" t="s">
+    <row r="100">
+      <c r="A100" s="16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="15">
-      <c r="A58" s="19" t="s">
+    <row r="101">
+      <c r="A101" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="15">
-      <c r="A59" s="19" t="s">
+    <row r="102">
+      <c r="A102" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="15"/>
-    <row r="61" ht="15" customHeight="1" s="15">
-      <c r="A61" s="17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="15">
-      <c r="A62" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="15">
-      <c r="A63" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="15">
-      <c r="A64" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="15">
-      <c r="A65" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="15"/>
-    <row r="67" ht="15" customHeight="1" s="15">
-      <c r="A67" s="18" t="s">
+    <row r="103">
+      <c r="A103" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="15"/>
-    <row r="69" ht="15" customHeight="1" s="15">
-      <c r="A69" s="17" t="s">
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="15">
-      <c r="A70" s="17" t="s">
+    <row r="106">
+      <c r="A106" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="15">
-      <c r="A71" s="17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="15">
-      <c r="A72" s="19" t="s">
+    <row r="107">
+      <c r="A107" s="16" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="16" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="15">
-      <c r="A73" s="19" t="s">
+    <row r="110">
+      <c r="A110" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="15"/>
-    <row r="75" ht="15" customHeight="1" s="15">
-      <c r="A75" s="17" t="s">
+    <row r="111">
+      <c r="A111" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="15">
-      <c r="A76" s="17" t="s">
+    <row r="112">
+      <c r="A112" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="15">
-      <c r="A77" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="15"/>
-    <row r="79" ht="15" customHeight="1" s="15">
-      <c r="A79" s="18" t="s">
+    <row r="113">
+      <c r="A113" s="16" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="16" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="116"/>
+    <row r="117">
+      <c r="A117" s="16" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="16" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="16" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="16" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="16" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123">
+      <c r="A123" s="16" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="16" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="16" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="16" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="16" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="16" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="15"/>
-    <row r="81" ht="15" customHeight="1" s="15">
-      <c r="A81" s="17" t="s">
+    <row r="134">
+      <c r="A134" s="16" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="15">
-      <c r="A82" s="19" t="s">
+    <row r="135"/>
+    <row r="136">
+      <c r="A136" s="16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="15">
-      <c r="A83" s="19" t="s">
+    <row r="137">
+      <c r="A137" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="15"/>
-    <row r="85" ht="15" customHeight="1" s="15">
-      <c r="A85" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="15">
-      <c r="A86" s="17" t="s">
+    <row r="138">
+      <c r="A138" s="16" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="15">
-      <c r="A87" s="19" t="s">
+    <row r="140">
+      <c r="A140" s="16" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="15">
-      <c r="A88" s="19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="15"/>
-    <row r="90" ht="15" customHeight="1" s="15">
-      <c r="A90" s="18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="15"/>
-    <row r="92" ht="15" customHeight="1" s="15">
-      <c r="A92" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="15">
-      <c r="A93" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="15">
-      <c r="A94" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="15">
-      <c r="A95" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" s="15">
-      <c r="A96" s="19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="15">
-      <c r="A97" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="15">
-      <c r="A98" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="15">
-      <c r="A99" s="19" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1" s="15"/>
-    <row r="101" ht="15" customHeight="1" s="15">
-      <c r="A101" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1" s="15">
-      <c r="A102" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" s="15"/>
-    <row r="104" ht="15" customHeight="1" s="15">
-      <c r="A104" s="17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1" s="15"/>
-    <row r="106" ht="15" customHeight="1" s="15">
-      <c r="A106" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1" s="15">
-      <c r="A107" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1" s="15">
-      <c r="A108" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="15"/>
-    <row r="110" ht="15" customHeight="1" s="15">
-      <c r="A110" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1" s="15">
-      <c r="A111" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1" s="15">
-      <c r="A112" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113" ht="15" customHeight="1" s="15">
-      <c r="A113" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1" s="15"/>
-    <row r="115" ht="15" customHeight="1" s="15">
-      <c r="A115" s="18" t="s">
+    <row r="141">
+      <c r="A141" s="16" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="142"/>
+    <row r="143">
+      <c r="A143" s="16" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="116" ht="15" customHeight="1" s="15"/>
-    <row r="117" ht="15" customHeight="1" s="15">
-      <c r="A117" s="17" t="s">
+    <row r="144">
+      <c r="A144" s="16" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1" s="15">
-      <c r="A118" s="17" t="s">
+    <row r="145"/>
+    <row r="146">
+      <c r="A146" s="16" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="15">
-      <c r="A119" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="120" ht="15" customHeight="1" s="15">
-      <c r="A120" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="121" ht="15" customHeight="1" s="15">
-      <c r="A121" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="15">
-      <c r="A122" s="17" t="s">
+    <row r="147">
+      <c r="A147" s="16" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="16" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="16" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="16" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1" s="15"/>
-    <row r="124" ht="15" customHeight="1" s="15">
-      <c r="A124" s="18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="125" ht="15" customHeight="1" s="15"/>
-    <row r="126" ht="15" customHeight="1" s="15">
-      <c r="A126" s="17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="127" ht="15" customHeight="1" s="15">
-      <c r="A127" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="128" ht="15" customHeight="1" s="15">
-      <c r="A128" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="129" ht="15" customHeight="1" s="15">
-      <c r="A129" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="130" ht="15" customHeight="1" s="15">
-      <c r="A130" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="131" ht="15" customHeight="1" s="15"/>
-    <row r="132" ht="15" customHeight="1" s="15">
-      <c r="A132" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="15"/>
-    <row r="134" ht="15" customHeight="1" s="15">
-      <c r="A134" s="18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1" s="15"/>
-    <row r="136" ht="15" customHeight="1" s="15">
-      <c r="A136" s="17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="137" ht="15" customHeight="1" s="15">
-      <c r="A137" s="19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="138" ht="15" customHeight="1" s="15">
-      <c r="A138" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="139" ht="15" customHeight="1" s="15">
-      <c r="A139" s="19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="140" ht="15" customHeight="1" s="15"/>
-    <row r="141" ht="15" customHeight="1" s="15">
-      <c r="A141" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="142" ht="15" customHeight="1" s="15">
-      <c r="A142" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="143" ht="15" customHeight="1" s="15">
-      <c r="A143" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="144" ht="15" customHeight="1" s="15"/>
-    <row r="145" ht="15" customHeight="1" s="15">
-      <c r="A145" s="18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="146" ht="15" customHeight="1" s="15"/>
-    <row r="147" ht="15" customHeight="1" s="15">
-      <c r="A147" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="148" ht="15" customHeight="1" s="15">
-      <c r="A148" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="149" ht="15" customHeight="1" s="15"/>
-    <row r="150" ht="15" customHeight="1" s="15">
-      <c r="A150" s="19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="151" ht="15" customHeight="1" s="15">
-      <c r="A151" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="152" ht="15" customHeight="1" s="15">
-      <c r="A152" s="19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="153" ht="15" customHeight="1" s="15">
-      <c r="A153" s="19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="154" ht="15" customHeight="1" s="15">
-      <c r="A154" s="19" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="155" ht="15" customHeight="1" s="15">
-      <c r="A155" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1" s="15">
-      <c r="A156" s="19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1" s="15">
-      <c r="A157" s="19" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="158" ht="15" customHeight="1" s="15"/>
-    <row r="159" ht="15" customHeight="1" s="15">
-      <c r="A159" s="18" t="s">
+    <row r="153">
+      <c r="A153" s="16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1" s="15"/>
-    <row r="161" ht="15" customHeight="1" s="15">
-      <c r="A161" s="17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="162" ht="15" customHeight="1" s="15">
-      <c r="A162" s="17" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="163" ht="15" customHeight="1" s="15">
-      <c r="A163" s="17" t="s">
-        <v>120</v>
+    <row r="154">
+      <c r="A154" s="16" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="155"/>
+    <row r="156">
+      <c r="A156" s="16" t="s">
+        <v>1052</v>
       </c>
     </row>
   </sheetData>
@@ -20534,7 +20747,7 @@
         <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>697</v>
+        <v>321</v>
       </c>
       <c r="D63" t="n">
         <v>21</v>
@@ -20634,7 +20847,7 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>699</v>
+        <v>336</v>
       </c>
       <c r="D68" t="n">
         <v>21</v>
@@ -20714,7 +20927,7 @@
         <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>697</v>
+        <v>321</v>
       </c>
       <c r="D72" t="n">
         <v>21</v>
@@ -21574,7 +21787,7 @@
         <v>5</v>
       </c>
       <c r="C118" t="s">
-        <v>877</v>
+        <v>325</v>
       </c>
       <c r="D118" t="n">
         <v>21</v>
@@ -21646,20 +21859,6 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>881</v>
-      </c>
-      <c r="B122" t="n">
-        <v>20</v>
-      </c>
-      <c r="C122" t="s">
-        <v>882</v>
-      </c>
-      <c r="G122" t="n">
-        <v>1000</v>
-      </c>
-    </row>
     <row r="123">
       <c r="A123" t="s">
         <v>883</v>
